--- a/Matches.xlsx
+++ b/Matches.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC498D81-1FB4-4E37-B76E-A72230C4CC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7982797A-A556-44B2-95DE-774BC09E7E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
   <si>
     <t>fecha</t>
   </si>
@@ -52,9 +52,6 @@
     <t>match_filter</t>
   </si>
   <si>
-    <t>localidad</t>
-  </si>
-  <si>
     <t>match</t>
   </si>
   <si>
@@ -67,23 +64,71 @@
     <t>Amistoso</t>
   </si>
   <si>
-    <t>visita</t>
-  </si>
-  <si>
-    <t>https://youtu.be/fE4Ma9vXx1w</t>
-  </si>
-  <si>
-    <t>Cantolao Arequipa</t>
-  </si>
-  <si>
-    <t>Juvenila Bellapampa</t>
+    <t>Tiznados FC</t>
+  </si>
+  <si>
+    <t>Distrital</t>
+  </si>
+  <si>
+    <t>Temperley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/NEaSJNpXzsk </t>
+  </si>
+  <si>
+    <t>Propio</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>False</t>
+  </si>
+  <si>
+    <t>Cantolao</t>
+  </si>
+  <si>
+    <t>ADEPA</t>
+  </si>
+  <si>
+    <t>White Star</t>
+  </si>
+  <si>
+    <t>FBC Pierola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/4A_U7duurO8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/y9JpXY4J4NI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/5qZ0gl1jhqg </t>
+  </si>
+  <si>
+    <t>FBC Aurora</t>
+  </si>
+  <si>
+    <t>Atl. Universidad</t>
+  </si>
+  <si>
+    <t>fecha 1</t>
+  </si>
+  <si>
+    <t>jornada</t>
+  </si>
+  <si>
+    <t>J. Bellapampa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/fE4Ma9vXx1w </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,6 +148,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -129,11 +180,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -415,108 +468,292 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.140625" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="17.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="7.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>46071</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <f>CONCATENATE(F2,A2)</f>
+        <v>146071</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>13</v>
       </c>
+      <c r="F2" s="5">
+        <v>1</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="5">
+        <v>0</v>
+      </c>
+      <c r="K2" t="str">
+        <f>CONCATENATE(I2,"_",J2)</f>
+        <v>J. Bellapampa_0</v>
+      </c>
+      <c r="L2" t="str">
+        <f>CONCATENATE( "vs ",I2)</f>
+        <v>vs J. Bellapampa</v>
+      </c>
+      <c r="M2" s="5">
+        <v>2</v>
+      </c>
+      <c r="N2" s="5">
+        <v>1</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>46071</v>
-      </c>
-      <c r="B2" s="2" t="str">
-        <f t="shared" ref="B2" si="0">CONCATENATE(E2,A2)</f>
-        <v>46071</v>
-      </c>
-      <c r="C2" s="3" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>46074</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="str">
+        <f>CONCATENATE(F3,A3)</f>
+        <v>046074</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2">
+      <c r="K3" t="str">
+        <f>CONCATENATE(I3,"_",J3)</f>
+        <v>Temperley_</v>
+      </c>
+      <c r="L3" t="str">
+        <f>CONCATENATE( "vs ",I3)</f>
+        <v>vs Temperley</v>
+      </c>
+      <c r="M3">
+        <v>5</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>46074</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="2" t="str">
+        <f t="shared" ref="C4:C6" si="0">CONCATENATE(F4,A4)</f>
+        <v>146074</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4">
         <v>1</v>
       </c>
-      <c r="J2" t="str">
-        <f>CONCATENATE(H2,"_",I2)</f>
-        <v>Juvenila Bellapampa_1</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
+        <f t="shared" ref="K4:K6" si="1">CONCATENATE(I4,"_",J4)</f>
+        <v>ADEPA_1</v>
+      </c>
+      <c r="L4" t="str">
+        <f t="shared" ref="L4:L6" si="2">CONCATENATE( "vs ",I4)</f>
+        <v>vs ADEPA</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>2</v>
+      </c>
+      <c r="O4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>46074</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>46074</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
         <v>15</v>
       </c>
-      <c r="L2" t="str">
-        <f t="shared" ref="L2" si="1">CONCATENATE( "vs ",H2)</f>
-        <v>vs Juvenila Bellapampa</v>
-      </c>
-      <c r="M2">
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="str">
+        <f t="shared" si="1"/>
+        <v>FBC Pierola_</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" si="2"/>
+        <v>vs FBC Pierola</v>
+      </c>
+      <c r="M5">
         <v>1</v>
       </c>
-      <c r="N2">
+      <c r="N5">
         <v>2</v>
+      </c>
+      <c r="O5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>46074</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>46074</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" t="str">
+        <f t="shared" si="1"/>
+        <v>Atl. Universidad_</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="2"/>
+        <v>vs Atl. Universidad</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{75E48457-E123-4A47-A866-977C26D3B551}"/>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{473ABD2C-6F54-49B6-A931-4DAF6AE08896}"/>
+    <hyperlink ref="D4" r:id="rId2" xr:uid="{9851E299-9FF1-485E-9BC4-F8EA129EEA6D}"/>
+    <hyperlink ref="D5" r:id="rId3" xr:uid="{B11D7526-21E8-40E0-ADE4-CB1FA5073E22}"/>
+    <hyperlink ref="D6" r:id="rId4" xr:uid="{6893FB00-92C8-4166-AD25-B61129E8163B}"/>
+    <hyperlink ref="D2" r:id="rId5" xr:uid="{F1985E59-87C8-4F74-91AA-7C6C2812945E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Matches.xlsx
+++ b/Matches.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7982797A-A556-44B2-95DE-774BC09E7E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC065EB2-A312-409A-A361-324B1753E794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -180,13 +180,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -474,7 +472,7 @@
     <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.7109375" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.140625" customWidth="1"/>
+    <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
@@ -529,8 +527,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>46071</v>
       </c>
       <c r="C2" s="2" t="str">
@@ -540,19 +538,19 @@
       <c r="D2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2">
         <v>1</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="str">
@@ -563,13 +561,13 @@
         <f>CONCATENATE( "vs ",I2)</f>
         <v>vs J. Bellapampa</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2">
         <v>2</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2">
         <v>1</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" t="s">
         <v>19</v>
       </c>
     </row>
